--- a/artfynd/A 1763-2025 artfynd.xlsx
+++ b/artfynd/A 1763-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122362912</v>
+        <v>122362891</v>
       </c>
       <c r="B2" t="n">
-        <v>57527</v>
+        <v>94947</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590398</v>
+        <v>590426</v>
       </c>
       <c r="R2" t="n">
-        <v>6441172</v>
+        <v>6441177</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122362891</v>
+        <v>122362912</v>
       </c>
       <c r="B3" t="n">
-        <v>94947</v>
+        <v>57527</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,31 +794,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590426</v>
+        <v>590398</v>
       </c>
       <c r="R3" t="n">
-        <v>6441177</v>
+        <v>6441172</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +874,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1763-2025 artfynd.xlsx
+++ b/artfynd/A 1763-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122362891</v>
+        <v>122362866</v>
       </c>
       <c r="B2" t="n">
-        <v>94947</v>
+        <v>57390</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590426</v>
+        <v>590412</v>
       </c>
       <c r="R2" t="n">
-        <v>6441177</v>
+        <v>6441107</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,13 +761,17 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Bearbetat barkborregran</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122362912</v>
+        <v>122362891</v>
       </c>
       <c r="B3" t="n">
-        <v>57527</v>
+        <v>94957</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,35 +802,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590398</v>
+        <v>590426</v>
       </c>
       <c r="R3" t="n">
-        <v>6441172</v>
+        <v>6441177</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,6 +878,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -892,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122362866</v>
+        <v>122362912</v>
       </c>
       <c r="B4" t="n">
-        <v>57390</v>
+        <v>57527</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,7 +935,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -940,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590412</v>
+        <v>590398</v>
       </c>
       <c r="R4" t="n">
-        <v>6441107</v>
+        <v>6441172</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,11 +981,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Bearbetat barkborregran</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 1763-2025 artfynd.xlsx
+++ b/artfynd/A 1763-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122362866</v>
+        <v>122362912</v>
       </c>
       <c r="B2" t="n">
-        <v>57390</v>
+        <v>57527</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,7 +713,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590412</v>
+        <v>590398</v>
       </c>
       <c r="R2" t="n">
-        <v>6441107</v>
+        <v>6441172</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,11 +759,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bearbetat barkborregran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122362891</v>
+        <v>122362866</v>
       </c>
       <c r="B3" t="n">
-        <v>94957</v>
+        <v>57390</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,31 +797,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590426</v>
+        <v>590412</v>
       </c>
       <c r="R3" t="n">
-        <v>6441177</v>
+        <v>6441107</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,13 +871,17 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bearbetat barkborregran</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122362912</v>
+        <v>122362891</v>
       </c>
       <c r="B4" t="n">
-        <v>57527</v>
+        <v>94957</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,35 +912,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590398</v>
+        <v>590426</v>
       </c>
       <c r="R4" t="n">
-        <v>6441172</v>
+        <v>6441177</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,6 +988,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1763-2025 artfynd.xlsx
+++ b/artfynd/A 1763-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122362912</v>
+        <v>122362866</v>
       </c>
       <c r="B2" t="n">
-        <v>57527</v>
+        <v>57395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,7 +713,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590398</v>
+        <v>590412</v>
       </c>
       <c r="R2" t="n">
-        <v>6441172</v>
+        <v>6441107</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +759,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Bearbetat barkborregran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122362866</v>
+        <v>122362912</v>
       </c>
       <c r="B3" t="n">
-        <v>57390</v>
+        <v>57532</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,7 +828,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -833,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590412</v>
+        <v>590398</v>
       </c>
       <c r="R3" t="n">
-        <v>6441107</v>
+        <v>6441172</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,11 +874,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bearbetat barkborregran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,7 +903,7 @@
         <v>122362891</v>
       </c>
       <c r="B4" t="n">
-        <v>94957</v>
+        <v>94969</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 1763-2025 artfynd.xlsx
+++ b/artfynd/A 1763-2025 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>122362891</v>
       </c>
       <c r="B4" t="n">
-        <v>94969</v>
+        <v>94974</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 1763-2025 artfynd.xlsx
+++ b/artfynd/A 1763-2025 artfynd.xlsx
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>100049</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -808,11 +803,6 @@
       <c r="E3" t="n">
         <v>103021</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Poecile montanus</t>
@@ -903,7 +893,7 @@
         <v>122362891</v>
       </c>
       <c r="B4" t="n">
-        <v>94974</v>
+        <v>94983</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,11 +907,6 @@
       </c>
       <c r="E4" t="n">
         <v>2180</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Blåmossa</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 1763-2025 artfynd.xlsx
+++ b/artfynd/A 1763-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122362866</v>
+        <v>122362891</v>
       </c>
       <c r="B2" t="n">
-        <v>57395</v>
+        <v>94996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2180</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590412</v>
+        <v>590426</v>
       </c>
       <c r="R2" t="n">
-        <v>6441107</v>
+        <v>6441177</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,17 +757,13 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bearbetat barkborregran</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122362912</v>
+        <v>122362866</v>
       </c>
       <c r="B3" t="n">
-        <v>57532</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,16 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -818,7 +820,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -828,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590398</v>
+        <v>590412</v>
       </c>
       <c r="R3" t="n">
-        <v>6441172</v>
+        <v>6441107</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,6 +866,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bearbetat barkborregran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122362891</v>
+        <v>122362912</v>
       </c>
       <c r="B4" t="n">
-        <v>94983</v>
+        <v>57536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -902,26 +909,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -929,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590426</v>
+        <v>590398</v>
       </c>
       <c r="R4" t="n">
-        <v>6441177</v>
+        <v>6441172</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +989,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1763-2025 artfynd.xlsx
+++ b/artfynd/A 1763-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122362891</v>
+        <v>122362866</v>
       </c>
       <c r="B2" t="n">
-        <v>94996</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590426</v>
+        <v>590412</v>
       </c>
       <c r="R2" t="n">
-        <v>6441177</v>
+        <v>6441107</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,13 +761,17 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Bearbetat barkborregran</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122362866</v>
+        <v>122362912</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>57536</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,7 +828,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -830,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590412</v>
+        <v>590398</v>
       </c>
       <c r="R3" t="n">
-        <v>6441107</v>
+        <v>6441172</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,11 +874,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bearbetat barkborregran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122362912</v>
+        <v>122362891</v>
       </c>
       <c r="B4" t="n">
-        <v>57536</v>
+        <v>95009</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,35 +912,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590398</v>
+        <v>590426</v>
       </c>
       <c r="R4" t="n">
-        <v>6441172</v>
+        <v>6441177</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,6 +988,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1763-2025 artfynd.xlsx
+++ b/artfynd/A 1763-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122362866</v>
+        <v>122362912</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>57536</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,7 +713,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590412</v>
+        <v>590398</v>
       </c>
       <c r="R2" t="n">
-        <v>6441107</v>
+        <v>6441172</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,11 +759,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bearbetat barkborregran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122362912</v>
+        <v>122362866</v>
       </c>
       <c r="B3" t="n">
-        <v>57536</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -828,7 +823,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -838,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590398</v>
+        <v>590412</v>
       </c>
       <c r="R3" t="n">
-        <v>6441172</v>
+        <v>6441107</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,6 +869,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bearbetat barkborregran</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 1763-2025 artfynd.xlsx
+++ b/artfynd/A 1763-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122362912</v>
+        <v>122362891</v>
       </c>
       <c r="B2" t="n">
-        <v>57536</v>
+        <v>95011</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590398</v>
+        <v>590426</v>
       </c>
       <c r="R2" t="n">
-        <v>6441172</v>
+        <v>6441177</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122362866</v>
+        <v>122362912</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>57536</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,7 +820,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -833,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590412</v>
+        <v>590398</v>
       </c>
       <c r="R3" t="n">
-        <v>6441107</v>
+        <v>6441172</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,11 +866,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bearbetat barkborregran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122362891</v>
+        <v>122362866</v>
       </c>
       <c r="B4" t="n">
-        <v>95009</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,31 +904,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590426</v>
+        <v>590412</v>
       </c>
       <c r="R4" t="n">
-        <v>6441177</v>
+        <v>6441107</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,13 +978,17 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bearbetat barkborregran</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1763-2025 artfynd.xlsx
+++ b/artfynd/A 1763-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122362891</v>
+        <v>122362912</v>
       </c>
       <c r="B2" t="n">
-        <v>95011</v>
+        <v>57536</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590426</v>
+        <v>590398</v>
       </c>
       <c r="R2" t="n">
-        <v>6441177</v>
+        <v>6441172</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122362912</v>
+        <v>122362866</v>
       </c>
       <c r="B3" t="n">
-        <v>57536</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,7 +823,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -830,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590398</v>
+        <v>590412</v>
       </c>
       <c r="R3" t="n">
-        <v>6441172</v>
+        <v>6441107</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,6 +869,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bearbetat barkborregran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122362866</v>
+        <v>122362891</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>95011</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,35 +912,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -940,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590412</v>
+        <v>590426</v>
       </c>
       <c r="R4" t="n">
-        <v>6441107</v>
+        <v>6441177</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,17 +982,13 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Bearbetat barkborregran</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1763-2025 artfynd.xlsx
+++ b/artfynd/A 1763-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122362912</v>
       </c>
       <c r="B2" t="n">
-        <v>57536</v>
+        <v>57537</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>122362866</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>122362891</v>
       </c>
       <c r="B4" t="n">
-        <v>95011</v>
+        <v>95012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 1763-2025 artfynd.xlsx
+++ b/artfynd/A 1763-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122362912</v>
+        <v>122362866</v>
       </c>
       <c r="B2" t="n">
-        <v>57537</v>
+        <v>57400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,7 +713,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590398</v>
+        <v>590412</v>
       </c>
       <c r="R2" t="n">
-        <v>6441172</v>
+        <v>6441107</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +759,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Bearbetat barkborregran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122362866</v>
+        <v>122362891</v>
       </c>
       <c r="B3" t="n">
-        <v>57400</v>
+        <v>95015</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,35 +802,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590412</v>
+        <v>590426</v>
       </c>
       <c r="R3" t="n">
-        <v>6441107</v>
+        <v>6441177</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,17 +872,13 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bearbetat barkborregran</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122362891</v>
+        <v>122362912</v>
       </c>
       <c r="B4" t="n">
-        <v>95012</v>
+        <v>57537</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,31 +909,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590426</v>
+        <v>590398</v>
       </c>
       <c r="R4" t="n">
-        <v>6441177</v>
+        <v>6441172</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +989,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
